--- a/Assessment Questions/CDE/DATA ENGINEERING FOUNDATION/Data Engineering Role/Introduction to Docker and Docker Installation/Docker (1).xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING FOUNDATION/Data Engineering Role/Introduction to Docker and Docker Installation/Docker (1).xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
